--- a/virtual-physics-lab/app/dl/NJC_Q1_timing.xlsx
+++ b/virtual-physics-lab/app/dl/NJC_Q1_timing.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -86,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -94,6 +96,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -656,7 +660,7 @@
       <c r="A6" s="5" t="n">
         <v>1.66</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>9.800000000000001</v>
       </c>
     </row>
@@ -664,7 +668,7 @@
       <c r="A7" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>10.9</v>
       </c>
     </row>
@@ -672,7 +676,7 @@
       <c r="A8" s="5" t="n">
         <v>4.97</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>15</v>
       </c>
     </row>
@@ -680,7 +684,7 @@
       <c r="A9" s="5" t="n">
         <v>7.49</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>18.2</v>
       </c>
     </row>
@@ -688,7 +692,7 @@
       <c r="A10" s="5" t="n">
         <v>9.99</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -696,7 +700,7 @@
       <c r="A11" s="5" t="n">
         <v>14.98</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>29.6</v>
       </c>
     </row>
@@ -766,19 +770,19 @@
       <c r="A6" s="5" t="n">
         <v>1.66</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>a = gradient</t>
         </is>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="8">
         <f>SLOPE(B6:B11,A6:A11)</f>
         <v/>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>s kΩ⁻¹</t>
         </is>
@@ -788,19 +792,19 @@
       <c r="A7" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>10.9</v>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>b = intercept</t>
         </is>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="8">
         <f>INTERCEPT(B6:B11,A6:A11)</f>
         <v/>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -810,19 +814,19 @@
       <c r="A8" s="5" t="n">
         <v>4.97</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>b/a</t>
         </is>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="8">
         <f>INTERCEPT(B6:B11,A6:A11)/SLOPE(B6:B11,A6:A11)</f>
         <v/>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>kΩ</t>
         </is>
@@ -832,19 +836,19 @@
       <c r="A9" s="5" t="n">
         <v>7.49</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>18.2</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>C = a/ln2 (bonus)</t>
         </is>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="8">
         <f>SLOPE(B6:B11,A6:A11)/LN(2)/1000</f>
         <v/>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -854,7 +858,7 @@
       <c r="A10" s="5" t="n">
         <v>9.99</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>22.3</v>
       </c>
     </row>
@@ -862,7 +866,7 @@
       <c r="A11" s="5" t="n">
         <v>14.98</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>29.6</v>
       </c>
     </row>
